--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570207657</v>
+        <v>46157.93105261766</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105261766</v>
+        <v>46157.93176280284</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176280284</v>
+        <v>46157.93401667196</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401667196</v>
+        <v>46157.93719702522</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719702522</v>
+        <v>46158.28217802855</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217802855</v>
+        <v>46158.29683988159</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29683988159</v>
+        <v>46158.29816733037</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29816733037</v>
+        <v>46158.33388913925</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388913925</v>
+        <v>46158.36858664973</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858664973</v>
+        <v>46158.37289385548</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
